--- a/ParaBank_QA_Documentation_GeetShrimali.xlsx
+++ b/ParaBank_QA_Documentation_GeetShrimali.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7abea124a1da4d12/Desktop/final_sprint/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{4DF81CCD-F805-4F03-BCFC-2F8823AE8589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C2913E2-76F6-42D6-A4DD-33090B175C22}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{4DF81CCD-F805-4F03-BCFC-2F8823AE8589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E4C1B81-1AC2-4D77-9375-7D0948ECCD75}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Plan" sheetId="1" r:id="rId1"/>
@@ -45,9 +45,6 @@
     <t>Project Overview</t>
   </si>
   <si>
-    <t>Comprehensive manual verification framework for ParaBank's core banking transactions, including account creation and fund transfer. This plan defines the manual test coverage, scenarios, and verification steps across the user interface and API layers.</t>
-  </si>
-  <si>
     <t>Testing Objectives</t>
   </si>
   <si>
@@ -1081,6 +1078,9 @@
   </si>
   <si>
     <t>13.8s</t>
+  </si>
+  <si>
+    <t>This project provides a comprehensive testing framework for the ParaBank application, covering core banking functionalities such as account creation and fund transfers. It includes manual test planning and automated UI, API, and end-to-end test execution using Robot Framework. This plan defines the manual test coverage, scenarios, and verification steps across the user interface and API layers.</t>
   </si>
 </sst>
 </file>
@@ -1294,6 +1294,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1306,10 +1310,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1326,6 +1326,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1621,105 +1625,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="3" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1745,163 +1749,163 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="E3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="F4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>268</v>
-      </c>
       <c r="D5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="G5" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G6" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="E7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G7" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1925,610 +1929,610 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="J3" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="G4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="J4" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="J5" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="F6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="J6" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="I7" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="J8" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="J9" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="J10" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="J11" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="I12" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>266</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="I14" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="J15" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="G16" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="J16" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="F17" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="J17" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="H18" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="F19" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="J19" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2550,172 +2554,172 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="E6" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2739,52 +2743,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="A1" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>151</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>153</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>155</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>157</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B7" s="8">
         <v>18</v>
@@ -2792,7 +2796,7 @@
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" s="8">
         <v>14</v>
@@ -2800,7 +2804,7 @@
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9" s="8">
         <v>4</v>
@@ -2808,7 +2812,7 @@
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B10" s="8">
         <v>0</v>
@@ -2816,7 +2820,7 @@
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B11" s="14">
         <v>0.77800000000000002</v>
@@ -2824,496 +2828,496 @@
     </row>
     <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="C13" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C14" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="H14" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="C15" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="H15" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="C16" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="H16" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="C17" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="H17" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="C18" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="H18" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="C19" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="H19" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="C23" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="C24" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="C26" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="C29" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="H29" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="C30" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="H30" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="C31" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="H31" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -3362,177 +3366,177 @@
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="I2" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>232</v>
-      </c>
       <c r="J2" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>181</v>
-      </c>
       <c r="K3" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>236</v>
-      </c>
       <c r="G4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" s="9" t="s">
+      <c r="J4" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>181</v>
-      </c>
       <c r="K4" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="E5" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>48</v>
-      </c>
       <c r="I5" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -3556,52 +3560,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1" s="26"/>
+      <c r="A1" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="18"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="19" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B8" s="18"/>
+      <c r="B8" s="20"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B9" s="10">
         <v>18</v>
@@ -3609,7 +3613,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B10" s="10">
         <v>18</v>
@@ -3617,7 +3621,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B11" s="10">
         <v>14</v>
@@ -3625,7 +3629,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B12" s="10">
         <v>4</v>
@@ -3633,7 +3637,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B13" s="10">
         <v>0</v>
@@ -3641,7 +3645,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B14" s="12">
         <f>B11/B10</f>
@@ -3649,58 +3653,58 @@
       </c>
     </row>
     <row r="16" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="B16" s="18"/>
+      <c r="A16" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B16" s="20"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="B21" s="18"/>
+      <c r="B21" s="20"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B22" s="8" t="s">
+    </row>
+    <row r="24" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="19" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="B24" s="18"/>
+      <c r="B24" s="20"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B25" s="10">
         <v>4</v>
@@ -3708,7 +3712,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B26" s="10">
         <v>1</v>
@@ -3716,7 +3720,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B27" s="13">
         <v>1</v>
@@ -3724,7 +3728,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B28" s="10">
         <v>2</v>
@@ -3732,93 +3736,93 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B29" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="B31" s="18"/>
+      <c r="A31" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="B31" s="20"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>207</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>209</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="B41" s="18"/>
+      <c r="B41" s="20"/>
     </row>
     <row r="42" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="B42" s="20"/>
+      <c r="A42" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="B42" s="22"/>
     </row>
     <row r="43" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="21"/>
-      <c r="B43" s="22"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="24"/>
     </row>
     <row r="44" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="23"/>
-      <c r="B44" s="24"/>
+      <c r="A44" s="25"/>
+      <c r="B44" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="8">
